--- a/templetes/温眼.xlsx
+++ b/templetes/温眼.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>一票通</t>
   </si>
@@ -38,7 +38,7 @@
     <t>寄售出库（随货同行）单</t>
   </si>
   <si>
-    <t>器械</t>
+    <t>salemode</t>
   </si>
   <si>
     <t>发货日期：</t>
@@ -89,6 +89,9 @@
     <t>金额</t>
   </si>
   <si>
+    <t>prod_row1</t>
+  </si>
+  <si>
     <t>小计</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
   </si>
   <si>
     <t>金额合计：</t>
+  </si>
+  <si>
+    <t>amount</t>
   </si>
 </sst>
 </file>
@@ -873,9 +879,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -891,7 +895,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -901,6 +905,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -955,14 +960,11 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1577,10 +1579,10 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="14"/>
-      <c r="L4" s="11"/>
+      <c r="L4" s="15"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:12">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6"/>
@@ -1591,11 +1593,11 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="16"/>
+      <c r="J5" s="17"/>
       <c r="K5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="15"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="A6" s="6"/>
@@ -1607,14 +1609,14 @@
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
-      <c r="J6" s="16"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="11"/>
+      <c r="L6" s="15"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:12">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1626,143 +1628,144 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:12">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="22"/>
+      <c r="A9" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="23"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:12">
-      <c r="A10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="22"/>
+      <c r="A10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="23"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:12">
-      <c r="A11" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="A11" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="27" t="str">
         <f>F11</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="28">
-        <f>SUM(L9:L9)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="29"/>
+        <v>amount</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="30"/>
       <c r="K11" s="12"/>
-      <c r="L11" s="31"/>
+      <c r="L11" s="32"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:12">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:12">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="35"/>
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18.75" customHeight="1" spans="1:12">
-      <c r="A14" s="33"/>
-      <c r="B14" s="35"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="37"/>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="6:6">
       <c r="F18" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="10">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="K3:L3"/>
@@ -1773,9 +1776,6 @@
     <mergeCell ref="D10:K10"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A12:L12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="I13:L14"/>
   </mergeCells>
   <pageMargins left="0.196527777777778" right="0.118055555555556" top="0.393055555555556" bottom="0" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" scale="81" orientation="landscape"/>
